--- a/AAII_Financials/Quarterly/ACI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ACI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
   <si>
     <t>ACI</t>
   </si>
@@ -656,431 +656,443 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46193</v>
+      </c>
+      <c r="E7" s="2">
         <v>46081</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45990</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45906</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45822</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45710</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45626</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45542</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45458</v>
-      </c>
-      <c r="L7" s="2">
-        <v>45346</v>
       </c>
       <c r="M7" s="2">
         <v>45346</v>
       </c>
       <c r="N7" s="2">
+        <v>45346</v>
+      </c>
+      <c r="O7" s="2">
         <v>45178</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45094</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44982</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44898</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44814</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44730</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44618</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44534</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44450</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44366</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44254</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44170</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44086</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44002</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43890</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43799</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43715</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43631</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43519</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43435</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43351</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>24941600</v>
+      </c>
+      <c r="E8" s="3">
         <v>20252200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>19123700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>18915800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>24880800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>18799500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>18774500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>18551500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>24265400</v>
-      </c>
-      <c r="L8" s="3">
-        <v>18339500</v>
       </c>
       <c r="M8" s="3">
         <v>18339500</v>
       </c>
       <c r="N8" s="3">
+        <v>18339500</v>
+      </c>
+      <c r="O8" s="3">
         <v>18290700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>24050200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>18265100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>18154900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>41229700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>23310300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>17383500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>16728400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>37775100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>21269400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>15772300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>15408900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>15757600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>22751600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>15436800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>14103200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>14176700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>18738400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>14016600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>13840400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>14024100</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>18303500</v>
+      </c>
+      <c r="E9" s="3">
         <v>14739200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13874900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>13809200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>18142500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13650500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13528100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13430200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>17526500</v>
-      </c>
-      <c r="L9" s="3">
-        <v>13275800</v>
       </c>
       <c r="M9" s="3">
         <v>13275800</v>
       </c>
       <c r="N9" s="3">
+        <v>13275800</v>
+      </c>
+      <c r="O9" s="3">
         <v>13249200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>17387500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12747500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13033200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>29680100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>16765300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12399200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>11898300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>26867100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>15078400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>11212800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>10900300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>11182700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>15980100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>11018800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>10108100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>10235200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>13498800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>9957900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>9988000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>10211300</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>6638100</v>
+      </c>
+      <c r="E10" s="3">
         <v>5513000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5248800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5106600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6738300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5149000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5246400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5121300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6738900</v>
-      </c>
-      <c r="L10" s="3">
-        <v>5063700</v>
       </c>
       <c r="M10" s="3">
         <v>5063700</v>
       </c>
       <c r="N10" s="3">
+        <v>5063700</v>
+      </c>
+      <c r="O10" s="3">
         <v>5041500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6662700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5517600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5121700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>11549600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6545000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4984300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4830100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>10908000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>6191000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4559500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4508600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4574900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>6771500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4418000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3995100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3941500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>5239600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4058700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3852400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3812800</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1115,8 +1127,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1126,17 +1139,17 @@
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3">
         <v>200</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
+      <c r="I12" s="3">
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1213,8 +1226,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1311,177 +1327,183 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>79200</v>
+      </c>
+      <c r="E14" s="3">
         <v>867000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>55500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>59300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>26700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>85600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>80800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>131200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>118100</v>
-      </c>
-      <c r="L14" s="3">
-        <v>72100</v>
       </c>
       <c r="M14" s="3">
         <v>72100</v>
       </c>
       <c r="N14" s="3">
+        <v>72100</v>
+      </c>
+      <c r="O14" s="3">
         <v>55200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>71700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>32600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>66500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>39700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>31100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>3700</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>31200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>12500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>49100</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>66700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>61700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>42700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>9500</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>591000</v>
+      </c>
+      <c r="E15" s="3">
         <v>-1321000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>397000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>400600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>572700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>-1297100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>392800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>391200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>552000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>387100</v>
       </c>
       <c r="M15" s="3">
         <v>387100</v>
       </c>
       <c r="N15" s="3">
+        <v>387100</v>
+      </c>
+      <c r="O15" s="3">
         <v>376300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>483900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>404500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>393300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>897500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>511600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>369000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>351200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>796400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>453400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>324500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>325100</v>
-      </c>
-      <c r="Z15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA15" s="3" t="s">
         <v>8</v>
@@ -1498,8 +1520,8 @@
       <c r="AE15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF15" s="3">
-        <v>0</v>
+      <c r="AF15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG15" s="3">
         <v>0</v>
@@ -1507,8 +1529,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1540,204 +1565,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24585500</v>
+      </c>
+      <c r="E17" s="3">
         <v>19909000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18570800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18522900</v>
       </c>
-      <c r="G17" s="3">
-        <v>24429400</v>
-      </c>
       <c r="H17" s="3">
+        <v>24406000</v>
+      </c>
+      <c r="I17" s="3">
         <v>18398600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>18164800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18121100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23715700</v>
-      </c>
-      <c r="L17" s="3">
-        <v>17840600</v>
       </c>
       <c r="M17" s="3">
         <v>17840600</v>
       </c>
       <c r="N17" s="3">
+        <v>17840600</v>
+      </c>
+      <c r="O17" s="3">
         <v>17784200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23368200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17832700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>17572500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>39938600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>22550200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>16719200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>16132500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>36602100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>20582300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>15974700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>15159000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>15244700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>21779800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>15155800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>13896600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>13617400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>18459600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>13727400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>13675500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>13892700</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>356100</v>
+      </c>
+      <c r="E18" s="3">
         <v>343200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>552900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>392900</v>
       </c>
-      <c r="G18" s="3">
-        <v>451400</v>
-      </c>
       <c r="H18" s="3">
+        <v>474800</v>
+      </c>
+      <c r="I18" s="3">
         <v>400900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>609700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>430400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>549700</v>
-      </c>
-      <c r="L18" s="3">
-        <v>498900</v>
       </c>
       <c r="M18" s="3">
         <v>498900</v>
       </c>
       <c r="N18" s="3">
+        <v>498900</v>
+      </c>
+      <c r="O18" s="3">
         <v>506500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>682000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>432400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>582400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1291100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>760100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>664300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>595900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1173000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>687100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-202400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>249900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>512900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>971800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>281000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>206600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>559300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>278800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>289200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>164900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>131400</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1772,498 +1804,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-14600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8600</v>
       </c>
-      <c r="G20" s="3">
-        <v>-28500</v>
-      </c>
       <c r="H20" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="I20" s="3">
         <v>-4400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>9100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-24000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>4000</v>
       </c>
       <c r="M20" s="3">
         <v>4000</v>
       </c>
       <c r="N20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="O20" s="3">
         <v>5000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-26000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>25200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>6300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>47500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>38300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>62400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>43500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>107200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>19200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>11400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-50400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>15900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>11100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>16100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>28300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>19200</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>950600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-963200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>946200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>784900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1052600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-891800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>997700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>812500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1125700</v>
-      </c>
-      <c r="L21" s="3">
-        <v>882000</v>
       </c>
       <c r="M21" s="3">
         <v>882000</v>
       </c>
       <c r="N21" s="3">
+        <v>882000</v>
+      </c>
+      <c r="O21" s="3">
         <v>877800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1191900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>843500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1001800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2276100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1314100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1119900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1024200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2118600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1234800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>270000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>632000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>873000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1428800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>640000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>606800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>935900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>805800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>703300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>594800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>553200</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>161900</v>
+      </c>
+      <c r="E22" s="3">
         <v>141100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>112200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>100100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>135600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>107600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>105200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>100000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>140800</v>
-      </c>
-      <c r="L22" s="3">
-        <v>108300</v>
       </c>
       <c r="M22" s="3">
         <v>108300</v>
       </c>
       <c r="N22" s="3">
+        <v>108300</v>
+      </c>
+      <c r="O22" s="3">
         <v>111900</v>
-      </c>
-      <c r="O22" s="3">
-        <v>148300</v>
       </c>
       <c r="P22" s="3">
         <v>148300</v>
       </c>
       <c r="Q22" s="3">
+        <v>148300</v>
+      </c>
+      <c r="R22" s="3">
         <v>84300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>228700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>138900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>108000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>111300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>262600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>153300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>113100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>115900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>128600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>180600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>140500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>154800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>177500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>225200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>168300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>213000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>194900</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>113700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-641000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>377700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>219700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>311400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>218200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>415100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>186500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>309900</v>
-      </c>
-      <c r="L23" s="3">
-        <v>314800</v>
       </c>
       <c r="M23" s="3">
         <v>314800</v>
       </c>
       <c r="N23" s="3">
+        <v>314800</v>
+      </c>
+      <c r="O23" s="3">
         <v>334400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>483300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>351500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>496400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1087600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>627500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>603800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>522900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>972800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>577300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-208300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>153200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>395700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>788100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>90100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>67700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>376700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>64700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>137000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-19800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-44300</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-160200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>84400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>51200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>75000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>46400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>41000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>69200</v>
-      </c>
-      <c r="L24" s="3">
-        <v>64300</v>
       </c>
       <c r="M24" s="3">
         <v>64300</v>
       </c>
       <c r="N24" s="3">
+        <v>64300</v>
+      </c>
+      <c r="O24" s="3">
         <v>67500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>66100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>40400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>120900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>260700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>143300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>148700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>98400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>232800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>132500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-64100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>29500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>111200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>201900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>22300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>12900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>81900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>15700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-5100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2360,204 +2408,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>84700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-480800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>293300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>168500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>236400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>171800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>400600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>145500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>240700</v>
-      </c>
-      <c r="L26" s="3">
-        <v>250500</v>
       </c>
       <c r="M26" s="3">
         <v>250500</v>
       </c>
       <c r="N26" s="3">
+        <v>250500</v>
+      </c>
+      <c r="O26" s="3">
         <v>266900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>417200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>311100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>375500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>826900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>484200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>455100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>424500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>740000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>444800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-144200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>123700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>284500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>586200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>67800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>54800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>294800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>49000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>139000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-14700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-32400</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>84700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-480800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>293300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>168500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>236400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>171800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>400600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>145500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>240700</v>
-      </c>
-      <c r="L27" s="3">
-        <v>250500</v>
       </c>
       <c r="M27" s="3">
         <v>250500</v>
       </c>
       <c r="N27" s="3">
+        <v>250500</v>
+      </c>
+      <c r="O27" s="3">
         <v>266900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>416500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>298400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>109100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>802800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>426700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>365800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>363100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>555100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>335200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-144200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>123700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>284500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>586200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>67800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>54800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>294800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>49000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>139000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-14700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-32400</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2654,8 +2711,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2725,8 +2785,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2743,17 +2803,20 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>60300</v>
       </c>
-      <c r="AH29" s="3" t="s">
+      <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2850,8 +2913,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2948,204 +3014,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E32" s="3">
         <v>14600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8600</v>
       </c>
-      <c r="G32" s="3">
-        <v>28500</v>
-      </c>
       <c r="H32" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I32" s="3">
         <v>4400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-9100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>24000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-4000</v>
       </c>
       <c r="M32" s="3">
         <v>-4000</v>
       </c>
       <c r="N32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="O32" s="3">
         <v>-5000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>26000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>6600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-25200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-6300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-47500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-38300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-62400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-43500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-107200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-19200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-11400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>50400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-15900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>5100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-11100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-16100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-28300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-19200</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>84700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-480800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>293300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>168500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>236400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>171800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>400600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>145500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>240700</v>
-      </c>
-      <c r="L33" s="3">
-        <v>250500</v>
       </c>
       <c r="M33" s="3">
         <v>250500</v>
       </c>
       <c r="N33" s="3">
+        <v>250500</v>
+      </c>
+      <c r="O33" s="3">
         <v>266900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>417200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>311100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>109100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>802800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>426700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>365800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>363100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>555100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>335200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-144200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>123700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>284500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>586200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>67800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>54800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>294800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>49000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>135600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>45600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-32400</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3242,209 +3317,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>84700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-480800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>293300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>168500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>236400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>171800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>400600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>145500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>240700</v>
-      </c>
-      <c r="L35" s="3">
-        <v>250500</v>
       </c>
       <c r="M35" s="3">
         <v>250500</v>
       </c>
       <c r="N35" s="3">
+        <v>250500</v>
+      </c>
+      <c r="O35" s="3">
         <v>266900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>417200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>311100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>109100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>802800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>426700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>365800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>363100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>555100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>335200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-144200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>123700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>284500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>586200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>67800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>54800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>294800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>49000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>135600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>45600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-32400</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46193</v>
+      </c>
+      <c r="E38" s="2">
         <v>46081</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45990</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45906</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45822</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45710</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45626</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45542</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45458</v>
-      </c>
-      <c r="L38" s="2">
-        <v>45346</v>
       </c>
       <c r="M38" s="2">
         <v>45346</v>
       </c>
       <c r="N38" s="2">
+        <v>45346</v>
+      </c>
+      <c r="O38" s="2">
         <v>45178</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45094</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44982</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44898</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44814</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44730</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44618</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44534</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44450</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44366</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44254</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44170</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44086</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44002</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43890</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43799</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43715</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43631</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43519</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43435</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43351</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3479,8 +3563,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3515,150 +3600,154 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>293400</v>
+      </c>
+      <c r="E41" s="3">
         <v>198600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>195100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>270600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>151000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>293600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>202300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>280000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>291100</v>
-      </c>
-      <c r="L41" s="3">
-        <v>188700</v>
       </c>
       <c r="M41" s="3">
         <v>188700</v>
       </c>
       <c r="N41" s="3">
+        <v>188700</v>
+      </c>
+      <c r="O41" s="3">
         <v>266100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>225200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>455800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4412300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3392400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3213100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2902000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2661000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2849800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2173800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1717000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1836100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2389600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2022200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>470700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>406400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>435300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>662100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>926100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>462600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1661900</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E42" s="3">
         <v>39700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>13600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>16200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>15400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>41300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>17800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>17200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>22000</v>
-      </c>
-      <c r="L42" s="3">
-        <v>23300</v>
       </c>
       <c r="M42" s="3">
         <v>23300</v>
       </c>
       <c r="N42" s="3">
+        <v>23300</v>
+      </c>
+      <c r="O42" s="3">
         <v>18200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>19000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>21400</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>8</v>
@@ -3672,8 +3761,8 @@
       <c r="U42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -3711,444 +3800,459 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1031900</v>
+      </c>
+      <c r="E43" s="3">
         <v>932600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1018900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>968800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>908900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>834800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>929000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>897600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>809400</v>
-      </c>
-      <c r="L43" s="3">
-        <v>724400</v>
       </c>
       <c r="M43" s="3">
         <v>724400</v>
       </c>
       <c r="N43" s="3">
+        <v>724400</v>
+      </c>
+      <c r="O43" s="3">
         <v>710100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>684300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>687600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>704800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>651700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>565300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>560600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>607400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>544700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>618700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>550900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>549500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>547100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>530000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>525300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>501200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>518600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>497400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>586200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>566900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>527900</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5192600</v>
+      </c>
+      <c r="E44" s="3">
         <v>5173900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5496700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5187500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4976300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4989000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5137200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5042700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4720000</v>
-      </c>
-      <c r="L44" s="3">
-        <v>4945200</v>
       </c>
       <c r="M44" s="3">
         <v>4945200</v>
       </c>
       <c r="N44" s="3">
+        <v>4945200</v>
+      </c>
+      <c r="O44" s="3">
         <v>5048300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4844900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4782000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5054900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4746400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4573200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4500800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4671000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4179100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4271900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4301300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4638000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4267100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4271600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4352500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4624200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4340300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4385400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4332800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4639500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4308100</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>354300</v>
+      </c>
+      <c r="E45" s="3">
         <v>2800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>372500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>409500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>365300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>61500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>379200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>409100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>365400</v>
-      </c>
-      <c r="L45" s="3">
-        <v>35600</v>
       </c>
       <c r="M45" s="3">
         <v>35600</v>
       </c>
       <c r="N45" s="3">
+        <v>35600</v>
+      </c>
+      <c r="O45" s="3">
         <v>378900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>287200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>20900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>513700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>474100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>326600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>403000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>440300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>414700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>313100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>418800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>420600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>374800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>309000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>382800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>447800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>336400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>361900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>404900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>443600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>347800</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6886700</v>
+      </c>
+      <c r="E46" s="3">
         <v>6715700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7096800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6852600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6416900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6559000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6665500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6646600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6207900</v>
-      </c>
-      <c r="L46" s="3">
-        <v>6287500</v>
       </c>
       <c r="M46" s="3">
         <v>6287500</v>
       </c>
       <c r="N46" s="3">
+        <v>6287500</v>
+      </c>
+      <c r="O46" s="3">
         <v>6421600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6060600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6270400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10685700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9264600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8678200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8366400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8379700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7988300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7377500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6988000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7444200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7578600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7132800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5731300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5979600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5630600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5906800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6250000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6112600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6845700</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>113000</v>
+      </c>
+      <c r="E47" s="3">
         <v>233200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>115300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>113700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>112300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>251900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>114600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>109600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>107400</v>
-      </c>
-      <c r="L47" s="3">
-        <v>224900</v>
       </c>
       <c r="M47" s="3">
         <v>224900</v>
       </c>
       <c r="N47" s="3">
+        <v>224900</v>
+      </c>
+      <c r="O47" s="3">
         <v>101600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>105100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>466300</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>8</v>
@@ -4162,8 +4266,8 @@
       <c r="U47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -4201,204 +4305,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16070000</v>
+      </c>
+      <c r="E48" s="3">
         <v>16006100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15882700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15838900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15882700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15964400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15727800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15574000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15527500</v>
-      </c>
-      <c r="L48" s="3">
-        <v>15551900</v>
       </c>
       <c r="M48" s="3">
         <v>15551900</v>
       </c>
       <c r="N48" s="3">
+        <v>15551900</v>
+      </c>
+      <c r="O48" s="3">
         <v>15387000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15238000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>15237800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>14942300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>14947500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>14978300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>15258000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>15172200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>15062400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>15152400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>15428300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>14829300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>14879200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>14875500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>15079300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>15058100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>15063100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>14943500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>9861300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>10143300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>10256900</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3283500</v>
+      </c>
+      <c r="E49" s="3">
         <v>3357100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3413300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3452100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3482100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3519000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3550300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3578900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3616400</v>
-      </c>
-      <c r="L49" s="3">
-        <v>3635500</v>
       </c>
       <c r="M49" s="3">
         <v>3635500</v>
       </c>
       <c r="N49" s="3">
+        <v>3635500</v>
+      </c>
+      <c r="O49" s="3">
         <v>3661700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3674200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3666400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3609800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3564500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3510600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3486000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3440500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3381500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3349600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3292100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3259700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3261100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3268800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3270500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3307200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3361200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3454500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4017800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4076600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4152200</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4495,8 +4608,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4593,106 +4709,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>563800</v>
+      </c>
+      <c r="E52" s="3">
         <v>238800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>585200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>593200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>575800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>205000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>607100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>619300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>617800</v>
-      </c>
-      <c r="L52" s="3">
-        <v>230700</v>
       </c>
       <c r="M52" s="3">
         <v>230700</v>
       </c>
       <c r="N52" s="3">
+        <v>230700</v>
+      </c>
+      <c r="O52" s="3">
         <v>750600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>739300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>235100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>976900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>977500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1052900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1012600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>943700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>912100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>902400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>889600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>786100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>750700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>710700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>654000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>646700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>643600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>676400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>647500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>649200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>562000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4789,106 +4911,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26917000</v>
+      </c>
+      <c r="E54" s="3">
         <v>26765900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27093300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>26850500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>26469800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>26755700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>26665300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>26528400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>26077000</v>
-      </c>
-      <c r="L54" s="3">
-        <v>26221100</v>
       </c>
       <c r="M54" s="3">
         <v>26221100</v>
       </c>
       <c r="N54" s="3">
+        <v>26221100</v>
+      </c>
+      <c r="O54" s="3">
         <v>26322500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>25817200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>26168200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>30214700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>28754100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>28220000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>28123000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>27936100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>27344300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>26781900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>26598000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>26319300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>26469600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>25987800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>24735100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>24991600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>24698500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>24981200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>20776600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>20981700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>21816800</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4923,8 +5051,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4959,596 +5088,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4087100</v>
+      </c>
+      <c r="E57" s="3">
         <v>4021200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4037700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3987900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3834100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4092700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4026100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4221900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3898200</v>
-      </c>
-      <c r="L57" s="3">
-        <v>4218200</v>
       </c>
       <c r="M57" s="3">
         <v>4218200</v>
       </c>
       <c r="N57" s="3">
+        <v>4218200</v>
+      </c>
+      <c r="O57" s="3">
         <v>4149700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4013200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4173100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3977700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4017800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3970300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4236800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4066100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3554200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3386300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3487300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3395000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3389800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3399800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2891100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3183200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2946600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3077900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2918700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3119200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2948200</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1485900</v>
+      </c>
+      <c r="E58" s="3">
         <v>1270700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1335600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1916700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1552400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>763100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>747600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>808400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>757600</v>
-      </c>
-      <c r="L58" s="3">
-        <v>962800</v>
       </c>
       <c r="M58" s="3">
         <v>962800</v>
       </c>
       <c r="N58" s="3">
+        <v>962800</v>
+      </c>
+      <c r="O58" s="3">
         <v>1307600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1242700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1740500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2025600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>826000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>825400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>828800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>82000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>211500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>214300</v>
-      </c>
-      <c r="X58" s="3">
-        <v>212400</v>
       </c>
       <c r="Y58" s="3">
         <v>212400</v>
       </c>
       <c r="Z58" s="3">
+        <v>212400</v>
+      </c>
+      <c r="AA58" s="3">
         <v>331600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>219100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>221400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>133300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>117100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>145000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>148800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>412600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>436500</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1414400</v>
+      </c>
+      <c r="E59" s="3">
         <v>413000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1148000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1105300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1208100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>275400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1029400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1039900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1213800</v>
-      </c>
-      <c r="L59" s="3">
-        <v>265200</v>
       </c>
       <c r="M59" s="3">
         <v>265200</v>
       </c>
       <c r="N59" s="3">
+        <v>265200</v>
+      </c>
+      <c r="O59" s="3">
         <v>1172500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1317700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>451200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7305700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3400700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3116600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3282900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3313100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3304000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3103600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3132500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2989900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3006300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3131400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2791800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2655700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2666000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2491900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2085200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2008900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2089300</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8175400</v>
+      </c>
+      <c r="E60" s="3">
         <v>7824000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7815300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8416700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7867900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7251000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7155100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7422400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7066000</v>
-      </c>
-      <c r="L60" s="3">
-        <v>7457700</v>
       </c>
       <c r="M60" s="3">
         <v>7457700</v>
       </c>
       <c r="N60" s="3">
+        <v>7457700</v>
+      </c>
+      <c r="O60" s="3">
         <v>7923500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7723100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8428800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>13309000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8244500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7912300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8348500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7461200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7069700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6704200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6832200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6597300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6727700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6750300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5904300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5972200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5729700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5714800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5152700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5540700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5474000</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14215100</v>
+      </c>
+      <c r="E61" s="3">
         <v>14026200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14096100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12650400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12762000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13419700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13462600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13394400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13385100</v>
-      </c>
-      <c r="L61" s="3">
-        <v>13276600</v>
       </c>
       <c r="M61" s="3">
         <v>13276600</v>
       </c>
       <c r="N61" s="3">
+        <v>13276600</v>
+      </c>
+      <c r="O61" s="3">
         <v>13353800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13288900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13220600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7091700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7106800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7121200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7136300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7915700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8129100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8145800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8101200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8328000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8460000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8484500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8493300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8615900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8628600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>9688600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10437600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>10565300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>11328900</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2285000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2357400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1859500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1856900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1831800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1711400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1952600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1963800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1958000</v>
-      </c>
-      <c r="L62" s="3">
-        <v>1687700</v>
       </c>
       <c r="M62" s="3">
         <v>1687700</v>
       </c>
       <c r="N62" s="3">
+        <v>1687700</v>
+      </c>
+      <c r="O62" s="3">
         <v>1997000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1989000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1714600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8415700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>8403600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8480500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8335100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8649400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8586500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8634400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8741200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8420200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8181200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7959000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8059400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7992900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>7994700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7523400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3735600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3485600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3651300</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5645,8 +5793,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5743,8 +5894,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5841,106 +5995,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25304300</v>
+      </c>
+      <c r="E66" s="3">
         <v>24929700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24591500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>23771000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>23245500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>23369800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>23299600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>23508100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>23163900</v>
-      </c>
-      <c r="L66" s="3">
-        <v>23473600</v>
       </c>
       <c r="M66" s="3">
         <v>23473600</v>
       </c>
       <c r="N66" s="3">
+        <v>23473600</v>
+      </c>
+      <c r="O66" s="3">
         <v>24105900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23817200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>24511800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>28816400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23754900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23514000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>23819900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>24026300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>23785300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>23484400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>23674600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>23345500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>23368900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>23193800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>22457000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>22581000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>22353000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>22926800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>19325900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>19591600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>20454200</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5975,8 +6135,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6073,8 +6234,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6171,8 +6335,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6213,22 +6380,22 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>45700</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>579300</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>612200</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>635400</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>1278500</v>
-      </c>
-      <c r="U70" s="3">
-        <v>1599100</v>
       </c>
       <c r="V70" s="3">
         <v>1599100</v>
@@ -6249,7 +6416,7 @@
         <v>1599100</v>
       </c>
       <c r="AB70" s="3">
-        <v>0</v>
+        <v>1599100</v>
       </c>
       <c r="AC70" s="3">
         <v>0</v>
@@ -6269,8 +6436,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6367,106 +6537,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1377400</v>
+      </c>
+      <c r="E72" s="3">
         <v>1378100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1936100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1721000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1637500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1487900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1403800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1073600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>998400</v>
-      </c>
-      <c r="L72" s="3">
-        <v>828200</v>
       </c>
       <c r="M72" s="3">
         <v>828200</v>
       </c>
       <c r="N72" s="3">
+        <v>828200</v>
+      </c>
+      <c r="O72" s="3">
         <v>356400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>159600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-185000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-417200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3239900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2972100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2564900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2187100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1846200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1624800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1263000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1481400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1432200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1174600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>592300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>524500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>469700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>174900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-431800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-567700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-613300</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6563,8 +6739,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6661,8 +6840,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6759,106 +6941,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1612700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1836200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2501800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3079500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3224300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3385900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3365700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3020300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2913100</v>
-      </c>
-      <c r="L76" s="3">
-        <v>2747500</v>
       </c>
       <c r="M76" s="3">
         <v>2747500</v>
       </c>
       <c r="N76" s="3">
+        <v>2747500</v>
+      </c>
+      <c r="O76" s="3">
         <v>2216600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2000000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1610700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>819000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4387000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4070600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3024600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2310700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1959900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1698400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1324300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1374700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1501600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1194900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2278100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2410600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2345500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2054400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1450700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1390100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1362600</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6955,209 +7143,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46193</v>
+      </c>
+      <c r="E80" s="2">
         <v>46081</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45990</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45906</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45822</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45710</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45626</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45542</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45458</v>
-      </c>
-      <c r="L80" s="2">
-        <v>45346</v>
       </c>
       <c r="M80" s="2">
         <v>45346</v>
       </c>
       <c r="N80" s="2">
+        <v>45346</v>
+      </c>
+      <c r="O80" s="2">
         <v>45178</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45094</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44982</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44898</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44814</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44730</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44618</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44534</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44450</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44366</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44254</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44170</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44086</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44002</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43890</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43799</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43715</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43631</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43519</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43435</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43351</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>84700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-480800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>293300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>168500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>236400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>171800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>400600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>145500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>240700</v>
-      </c>
-      <c r="L81" s="3">
-        <v>250500</v>
       </c>
       <c r="M81" s="3">
         <v>250500</v>
       </c>
       <c r="N81" s="3">
+        <v>250500</v>
+      </c>
+      <c r="O81" s="3">
         <v>266900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>417200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>311100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>109100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>802800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>426700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>365800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>363100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>555100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>335200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-144200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>123700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>284500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>586200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>67800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>54800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>294800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>49000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>135600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>45600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-32400</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7192,106 +7389,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>772000</v>
+      </c>
+      <c r="E83" s="3">
         <v>198700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>569600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>567500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>744900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>217900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>557400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>556900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>718800</v>
-      </c>
-      <c r="L83" s="3">
-        <v>298800</v>
       </c>
       <c r="M83" s="3">
         <v>298800</v>
       </c>
       <c r="N83" s="3">
+        <v>298800</v>
+      </c>
+      <c r="O83" s="3">
         <v>550700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>731100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>365400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>421100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>959800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>547700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>408100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>390000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>883200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>504200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>365200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>362900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>348700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>460100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>409400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>384300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>381700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>515900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>398000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>401600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>402600</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7388,8 +7589,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7486,8 +7690,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7584,8 +7791,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7682,8 +7892,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7780,106 +7993,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>728900</v>
+      </c>
+      <c r="E89" s="3">
         <v>717100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>367600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>527600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>754400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>758500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>548000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>413200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>960900</v>
-      </c>
-      <c r="L89" s="3">
-        <v>928700</v>
       </c>
       <c r="M89" s="3">
         <v>928700</v>
       </c>
       <c r="N89" s="3">
+        <v>928700</v>
+      </c>
+      <c r="O89" s="3">
         <v>509600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>838300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>781900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>419900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1652100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>991900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>730600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>645100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2137700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1059000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>906500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>275200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>628900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2091900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>516900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>302200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>282100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>802700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>618800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-122200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>279700</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7914,106 +8133,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-522100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-426600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-462300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-365900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-584600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-484500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-494400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-409300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-543000</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-496300</v>
       </c>
       <c r="M91" s="3">
         <v>-496300</v>
       </c>
       <c r="N91" s="3">
+        <v>-496300</v>
+      </c>
+      <c r="O91" s="3">
         <v>-461800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-622500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-587000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-506200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-446900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-613800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-390100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-393900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-309100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-513400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-547200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-380100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-300600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-402300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-391400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-367400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-354200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-362100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-445700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-285700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-281700</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8110,8 +8333,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8208,106 +8434,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-507700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-394000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-447500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-363800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-474100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-475300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-491200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-387300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-538000</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-417900</v>
       </c>
       <c r="M94" s="3">
         <v>-417900</v>
       </c>
       <c r="N94" s="3">
+        <v>-417900</v>
+      </c>
+      <c r="O94" s="3">
         <v>-436200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-453900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-498600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-501000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-977700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-551400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-361800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-386600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-790500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-493000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-627700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-257200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-287700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-399400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-353100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-333100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>601700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-294000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>273800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-272400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>189400</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8342,28 +8574,29 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E96" s="3">
         <v>76000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>77100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>83900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>85700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>86600</v>
-      </c>
-      <c r="I96" s="3">
-        <v>69500</v>
       </c>
       <c r="J96" s="3">
         <v>69500</v>
@@ -8372,47 +8605,47 @@
         <v>69500</v>
       </c>
       <c r="L96" s="3">
-        <v>69100</v>
+        <v>69500</v>
       </c>
       <c r="M96" s="3">
         <v>69100</v>
       </c>
       <c r="N96" s="3">
-        <v>69000</v>
+        <v>69100</v>
       </c>
       <c r="O96" s="3">
         <v>69000</v>
       </c>
       <c r="P96" s="3">
+        <v>69000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>64200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-64200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-126700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-63000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-58400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-56000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-93000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-46500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-46400</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -8440,8 +8673,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8538,8 +8774,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8636,8 +8875,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8734,106 +8976,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-129200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-321000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-44100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-422900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-191800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-134500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-37000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-320800</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-544800</v>
       </c>
       <c r="M100" s="3">
         <v>-544800</v>
       </c>
       <c r="N100" s="3">
+        <v>-544800</v>
+      </c>
+      <c r="O100" s="3">
         <v>-36100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-615000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4239800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1101000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-226600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-129500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-127800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-447300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-214400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-109200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-397900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-563200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>26200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-106900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-101500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-17200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1132800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-762700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-411000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-789100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-46900</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8876,8 +9124,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -8930,102 +9178,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-74100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>119700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-142600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>91400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-77700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-11100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>102100</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-34000</v>
       </c>
       <c r="M102" s="3">
         <v>-34000</v>
       </c>
       <c r="N102" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="O102" s="3">
         <v>37300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-230600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3956500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1019900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>447800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>311000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>241000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-188800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1132800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>456800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-119100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-545200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>367400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1585600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>62300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-48100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-249000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-254000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>481600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1183700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>422200</v>
       </c>
     </row>
